--- a/doc/testplan.xlsx
+++ b/doc/testplan.xlsx
@@ -5,15 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\vending_machine\Информация про проект\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\vending_machine\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F437864-92B8-45F8-A5AE-2022A9ECF85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CE39D-E783-4253-BDAA-9CE9A81F6AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="user_tests" sheetId="1" r:id="rId1"/>
+    <sheet name="register_tests" sheetId="2" r:id="rId2"/>
+    <sheet name="emergency_tests" sheetId="3" r:id="rId3"/>
+    <sheet name="integration_tests" sheetId="4" r:id="rId4"/>
+    <sheet name="errors_tests" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="106">
   <si>
     <t>Директория</t>
   </si>
@@ -46,12 +50,6 @@
   </si>
   <si>
     <t>Результат</t>
-  </si>
-  <si>
-    <t>Тесты пользовательского интерфейса</t>
-  </si>
-  <si>
-    <t>tb/user_srs/user_tests/</t>
   </si>
   <si>
     <t>Проверка корректной работы пользовательского интерфейса при внесении одной монеты (рубли).</t>
@@ -114,12 +112,6 @@
     <t>Обнаружен баг: сигнал item_empty не поднимается, когда товар закончился</t>
   </si>
   <si>
-    <t>Тесты регистрового интерфейса</t>
-  </si>
-  <si>
-    <t>tb/register_srs/register_tests/</t>
-  </si>
-  <si>
     <t>check_after_reset_test</t>
   </si>
   <si>
@@ -163,12 +155,6 @@
 Чтение регистров vend_item выдает неправильную информацию</t>
   </si>
   <si>
-    <t>Тесты сигналов сбоя</t>
-  </si>
-  <si>
-    <t>tb/emergency_srs/emergency_tests/</t>
-  </si>
-  <si>
     <t>check_alarm_test</t>
   </si>
   <si>
@@ -181,12 +167,6 @@
 4) Проверка появления сигнала alarm</t>
   </si>
   <si>
-    <t>Тесты взаимодействия нескольких интерфейсов</t>
-  </si>
-  <si>
-    <t>tb/integration_srs/integration_tests/</t>
-  </si>
-  <si>
     <t>client_session_after_change_price_test</t>
   </si>
   <si>
@@ -290,9 +270,6 @@
   </si>
   <si>
     <t>Требуется уточнение документации: поведение автомата при чтении после сигнала сбоя (должно ли выводится deadbeef?)</t>
-  </si>
-  <si>
-    <t>Тесты обработки ошибок</t>
   </si>
   <si>
     <t>Проверка реакции системы на недопустимый client_id</t>
@@ -434,12 +411,27 @@
   <si>
     <t>confirm_timeout_refund_test</t>
   </si>
+  <si>
+    <t>tb/tests/register_tests/</t>
+  </si>
+  <si>
+    <t>tb/tests/emergency_tests/</t>
+  </si>
+  <si>
+    <t>tb/tests/integration_tests/</t>
+  </si>
+  <si>
+    <t>tb/tests/user_tests/</t>
+  </si>
+  <si>
+    <t>Количество запусков</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -494,6 +486,13 @@
       <family val="1"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -509,7 +508,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -533,19 +532,38 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="8"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -577,11 +595,17 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -863,19 +887,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.5703125" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
     <col min="5" max="5" width="69.7109375" customWidth="1"/>
     <col min="6" max="6" width="17.28515625" customWidth="1"/>
     <col min="7" max="7" width="52.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -891,6 +916,415 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+    </row>
+    <row r="12" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="2"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
+    </row>
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="2"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="2"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="2"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="10"/>
+    </row>
+    <row r="31" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="2"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+    </row>
+    <row r="32" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4D5B730-83B0-4FB8-B030-FAC7931BD69B}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" customWidth="1"/>
+    <col min="5" max="5" width="60.140625" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
@@ -898,645 +1332,628 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-    </row>
-    <row r="3" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D2D84E2-6E6C-4C95-BFBA-79F6D7AA113B}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="3" max="3" width="29.28515625" customWidth="1"/>
+    <col min="4" max="4" width="29" customWidth="1"/>
+    <col min="5" max="5" width="65.28515625" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93627C58-502E-4982-BCB6-04125B09DD61}">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.85546875" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2"/>
+    </row>
+    <row r="3" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98B5287C-B551-4260-A2B3-B971BE4E5E7A}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="54.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="150" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-    </row>
-    <row r="10" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A15" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-    </row>
-    <row r="16" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-    </row>
-    <row r="24" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="112.5" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="75" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="80.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="G9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="A23:G23"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/doc/testplan.xlsx
+++ b/doc/testplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\vending_machine\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CE39D-E783-4253-BDAA-9CE9A81F6AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690DEBEC-7D68-465F-B0A0-499CC87CC341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user_tests" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="106">
   <si>
     <t>Директория</t>
   </si>
@@ -1307,9 +1307,10 @@
     <col min="5" max="5" width="60.140625" customWidth="1"/>
     <col min="6" max="6" width="19.42578125" customWidth="1"/>
     <col min="7" max="7" width="36.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,6 +1331,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
@@ -1354,7 +1358,7 @@
       <c r="G2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1380,7 +1384,7 @@
       <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1406,7 +1410,7 @@
       <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1427,9 +1431,10 @@
     <col min="5" max="5" width="65.28515625" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.85546875" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1450,6 +1455,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1474,7 +1482,7 @@
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1495,9 +1503,10 @@
     <col min="5" max="5" width="52.42578125" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1518,6 +1527,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
@@ -1542,7 +1554,7 @@
       <c r="G2" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="12">
         <v>1</v>
       </c>
       <c r="I2" s="2"/>
@@ -1569,7 +1581,7 @@
       <c r="G3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1595,7 +1607,7 @@
       <c r="G4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1621,7 +1633,7 @@
       <c r="G5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1647,7 +1659,7 @@
       <c r="G6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1673,7 +1685,7 @@
       <c r="G7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1699,8 +1711,8 @@
       <c r="G8" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="H8">
-        <v>1</v>
+      <c r="H8" s="12">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1720,9 +1732,10 @@
     <col min="5" max="5" width="55.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="54.28515625" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1743,6 +1756,9 @@
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
@@ -1767,7 +1783,7 @@
       <c r="G2" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1793,7 +1809,7 @@
       <c r="G3" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1819,7 +1835,7 @@
       <c r="G4" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1845,7 +1861,7 @@
       <c r="G5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1871,7 +1887,7 @@
       <c r="G6" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1897,7 +1913,7 @@
       <c r="G7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1923,7 +1939,7 @@
       <c r="G8" s="10" t="s">
         <v>89</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="12">
         <v>1</v>
       </c>
     </row>
@@ -1949,7 +1965,7 @@
       <c r="G9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="12">
         <v>1</v>
       </c>
     </row>

--- a/doc/testplan.xlsx
+++ b/doc/testplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SV\vending_machine\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690DEBEC-7D68-465F-B0A0-499CC87CC341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EBCD1A6-251D-40D7-BACA-860DB3C4C22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="user_tests" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="113">
   <si>
     <t>Директория</t>
   </si>
@@ -225,9 +225,6 @@
     <t>Новых багов не найдено (завершается с ошибками)</t>
   </si>
   <si>
-    <t>client_session_with_interrupt_test</t>
-  </si>
-  <si>
     <t>Проверка поведения системы при возникновении прерывания во время пользовательской сессии</t>
   </si>
   <si>
@@ -240,9 +237,6 @@
     <t>Обнаружен баг: пользовательская сессия не прекращается после появления сигнала сбоя</t>
   </si>
   <si>
-    <t>write_register_with_interrupt_test</t>
-  </si>
-  <si>
     <t>Проверка поведения системы при возникновении прерывания во время записи в регистры</t>
   </si>
   <si>
@@ -253,9 +247,6 @@
   </si>
   <si>
     <t>Обнаружен баг: запись в регистры продолжается после сигнала сбоя</t>
-  </si>
-  <si>
-    <t>read_register_with_interrupt_test</t>
   </si>
   <si>
     <t>Проверка поведения системы при возникновении прерывания во время чтения информации из регистров</t>
@@ -425,6 +416,40 @@
   </si>
   <si>
     <t>Количество запусков</t>
+  </si>
+  <si>
+    <t>buy_for_dollars_after_change_exchange_rate_test</t>
+  </si>
+  <si>
+    <t>Проверка корректности покупки за доллары после изменения курса валют</t>
+  </si>
+  <si>
+    <t>1) Сброс устройства
+2) Запись случайного значения в поле exchange_rate регистроа vend_cfg
+3) Покупка товара за доллары</t>
+  </si>
+  <si>
+    <t>Успешно завершен</t>
+  </si>
+  <si>
+    <t>buy_for_euros_after_change_exchange_rate_test</t>
+  </si>
+  <si>
+    <t>Проверка корректности покупки за евро после изменения курса валют</t>
+  </si>
+  <si>
+    <t>1) Сброс устройства
+2) Запись случайного значения в поле exchange_rate регистроа vend_cfg
+3) Покупка товара за евро</t>
+  </si>
+  <si>
+    <t>client_session_with_emergency_test</t>
+  </si>
+  <si>
+    <t>write_registers_with_emergency_test</t>
+  </si>
+  <si>
+    <t>read_registers_with_emergency_test</t>
   </si>
 </sst>
 </file>
@@ -563,7 +588,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,6 +631,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,15 +951,15 @@
         <v>6</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -954,10 +982,10 @@
     </row>
     <row r="3" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>12</v>
@@ -980,10 +1008,10 @@
     </row>
     <row r="4" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -992,7 +1020,7 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>10</v>
@@ -1006,10 +1034,10 @@
     </row>
     <row r="5" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>15</v>
@@ -1018,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
@@ -1032,10 +1060,10 @@
     </row>
     <row r="6" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>16</v>
@@ -1058,10 +1086,10 @@
     </row>
     <row r="7" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>18</v>
@@ -1310,7 +1338,7 @@
     <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1333,12 +1361,12 @@
         <v>6</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>21</v>
@@ -1364,7 +1392,7 @@
     </row>
     <row r="3" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>25</v>
@@ -1390,7 +1418,7 @@
     </row>
     <row r="4" spans="1:8" ht="112.5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
@@ -1434,7 +1462,7 @@
     <col min="8" max="8" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1457,12 +1485,12 @@
         <v>6</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>32</v>
@@ -1493,11 +1521,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93627C58-502E-4982-BCB6-04125B09DD61}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.85546875" customWidth="1"/>
+    <col min="2" max="2" width="55.42578125" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" customWidth="1"/>
     <col min="4" max="4" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="52.42578125" customWidth="1"/>
@@ -1506,7 +1534,7 @@
     <col min="8" max="8" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1529,12 +1557,12 @@
         <v>6</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
@@ -1549,7 +1577,7 @@
         <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5" t="s">
         <v>38</v>
@@ -1561,7 +1589,7 @@
     </row>
     <row r="3" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>39</v>
@@ -1585,27 +1613,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="4" t="s">
-        <v>46</v>
+      <c r="G4" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="H4" s="12">
         <v>1</v>
@@ -1613,105 +1641,157 @@
     </row>
     <row r="5" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>47</v>
+        <v>100</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>48</v>
+        <v>108</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>49</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H5" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H6" s="12">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="131.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>56</v>
+        <v>47</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="93.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="G10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="12">
+      <c r="H10" s="12">
         <v>0</v>
       </c>
     </row>
@@ -1735,7 +1815,7 @@
     <col min="8" max="8" width="14.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1758,30 +1838,30 @@
         <v>6</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H2" s="12">
         <v>1</v>
@@ -1789,25 +1869,25 @@
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H3" s="12">
         <v>1</v>
@@ -1815,25 +1895,25 @@
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H4" s="12">
         <v>1</v>
@@ -1841,25 +1921,25 @@
     </row>
     <row r="5" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H5" s="12">
         <v>1</v>
@@ -1867,25 +1947,25 @@
     </row>
     <row r="6" spans="1:8" ht="93.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H6" s="12">
         <v>1</v>
@@ -1893,19 +1973,19 @@
     </row>
     <row r="7" spans="1:8" ht="131.25" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>10</v>
@@ -1919,25 +1999,25 @@
     </row>
     <row r="8" spans="1:8" ht="150" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H8" s="12">
         <v>1</v>
@@ -1945,19 +2025,19 @@
     </row>
     <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
